--- a/data/trans_camb/LAWTONB_2R2-Provincia-trans_camb.xlsx
+++ b/data/trans_camb/LAWTONB_2R2-Provincia-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-13,78; 24,82</t>
+          <t>-15,12; 25,42</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-19,36; 17,39</t>
+          <t>-20,78; 17,15</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>5,21; 40,72</t>
+          <t>4,9; 40,31</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>14,97; 54,9</t>
+          <t>15,2; 55,2</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>6,26; 47,92</t>
+          <t>4,55; 47,39</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>7,89; 42,92</t>
+          <t>6,2; 40,39</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>6,46; 35,15</t>
+          <t>6,34; 34,97</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-1,09; 28,45</t>
+          <t>0,32; 28,81</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>12,46; 37,56</t>
+          <t>12,88; 36,96</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-41,63; 168,94</t>
+          <t>-44,68; 196,25</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-57,2; 134,57</t>
+          <t>-57,65; 106,28</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>12,24; 293,54</t>
+          <t>11,11; 297,26</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>40,53; 397,05</t>
+          <t>35,33; 397,47</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>15,67; 331,52</t>
+          <t>9,12; 337,83</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>18,05; 316,88</t>
+          <t>16,9; 287,14</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>17,71; 199,83</t>
+          <t>19,5; 189,06</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-5,54; 162,75</t>
+          <t>0,91; 184,96</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>33,0; 220,4</t>
+          <t>36,85; 224,48</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-11,13; 20,51</t>
+          <t>-10,52; 21,51</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-23,63; 3,75</t>
+          <t>-22,94; 3,71</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-19,75; 8,72</t>
+          <t>-17,75; 10,59</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>7,25; 32,64</t>
+          <t>6,77; 31,89</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-1,66; 24,05</t>
+          <t>-3,67; 23,23</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>7,72; 30,58</t>
+          <t>9,12; 30,86</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>2,1; 22,91</t>
+          <t>3,47; 23,3</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-7,34; 12,14</t>
+          <t>-7,51; 11,67</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>3,26; 20,16</t>
+          <t>2,17; 19,66</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-36,69; 122,51</t>
+          <t>-35,36; 135,05</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-69,57; 27,15</t>
+          <t>-67,09; 28,39</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-58,44; 58,53</t>
+          <t>-54,2; 69,23</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>23,79; 194,37</t>
+          <t>24,88; 194,06</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-5,89; 146,3</t>
+          <t>-13,48; 130,55</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>23,65; 188,49</t>
+          <t>27,42; 183,09</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>8,03; 119,16</t>
+          <t>11,66; 124,66</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-25,84; 65,26</t>
+          <t>-26,21; 62,72</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>11,23; 110,5</t>
+          <t>7,25; 106,15</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-9,67; 21,78</t>
+          <t>-10,82; 20,56</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-11,94; 16,66</t>
+          <t>-12,45; 17,07</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1,93; 29,07</t>
+          <t>1,78; 29,64</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-24,58; 5,23</t>
+          <t>-25,51; 7,43</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-36,32; -5,44</t>
+          <t>-36,53; -5,94</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-5,42; 22,24</t>
+          <t>-4,42; 22,21</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-15,98; 6,85</t>
+          <t>-15,13; 7,29</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-22,47; -0,98</t>
+          <t>-22,23; -1,22</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0,2; 19,93</t>
+          <t>0,35; 20,41</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-32,95; 185,04</t>
+          <t>-44,49; 156,66</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-40,57; 133,4</t>
+          <t>-43,43; 144,74</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>5,72; 231,15</t>
+          <t>1,83; 256,08</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-50,15; 14,39</t>
+          <t>-50,15; 22,69</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-73,28; -14,42</t>
+          <t>-72,08; -15,36</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-10,46; 65,9</t>
+          <t>-8,28; 66,52</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-39,85; 23,84</t>
+          <t>-39,0; 24,45</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-57,08; -1,12</t>
+          <t>-56,8; -5,61</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-0,82; 71,77</t>
+          <t>1,11; 76,14</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-12,29; 21,81</t>
+          <t>-11,03; 20,97</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-21,15; 10,69</t>
+          <t>-19,92; 10,08</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-19,69; 8,76</t>
+          <t>-17,77; 9,62</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-12,28; 17,79</t>
+          <t>-13,13; 18,64</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-26,71; 4,77</t>
+          <t>-27,19; 4,82</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-21,68; 3,9</t>
+          <t>-21,56; 2,88</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-7,17; 15,8</t>
+          <t>-7,43; 16,73</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-19,13; 2,0</t>
+          <t>-19,39; 2,49</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-16,34; 2,5</t>
+          <t>-16,09; 2,94</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-34,7; 120,78</t>
+          <t>-31,37; 121,33</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-58,16; 59,5</t>
+          <t>-55,64; 47,99</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-51,64; 49,54</t>
+          <t>-48,36; 49,44</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-24,7; 49,96</t>
+          <t>-24,48; 52,65</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-53,35; 13,52</t>
+          <t>-53,05; 16,54</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-39,63; 12,38</t>
+          <t>-40,29; 8,47</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-16,07; 52,94</t>
+          <t>-17,77; 54,24</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-46,98; 6,23</t>
+          <t>-45,83; 8,25</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-38,25; 9,47</t>
+          <t>-36,43; 10,95</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-24,02; 21,08</t>
+          <t>-24,62; 21,8</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-37,1; -1,68</t>
+          <t>-38,44; -1,8</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-23,26; 13,72</t>
+          <t>-24,35; 12,89</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-7,91; 33,76</t>
+          <t>-8,12; 34,51</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-13,12; 30,15</t>
+          <t>-11,31; 29,38</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-27,22; 6,17</t>
+          <t>-25,66; 7,07</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-8,99; 23,28</t>
+          <t>-8,99; 22,59</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-19,04; 10,94</t>
+          <t>-17,73; 12,65</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-18,83; 6,56</t>
+          <t>-19,81; 5,52</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-61,82; 116,2</t>
+          <t>-63,1; 136,29</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-88,4; 3,69</t>
+          <t>-88,0; 2,08</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-54,39; 84,36</t>
+          <t>-56,53; 78,04</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-16,62; 133,51</t>
+          <t>-16,78; 127,5</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-24,59; 119,75</t>
+          <t>-23,5; 107,73</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-52,8; 21,64</t>
+          <t>-49,46; 31,32</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-23,42; 84,96</t>
+          <t>-21,97; 87,57</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-46,1; 43,07</t>
+          <t>-41,04; 48,21</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-43,3; 27,49</t>
+          <t>-45,19; 22,38</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-21,76; 16,86</t>
+          <t>-21,98; 16,43</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-24,52; 11,48</t>
+          <t>-26,78; 10,12</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-14,75; 16,93</t>
+          <t>-14,61; 18,86</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-25,02; 5,71</t>
+          <t>-25,51; 5,5</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-24,35; 12,44</t>
+          <t>-21,56; 13,51</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-2,75; 24,46</t>
+          <t>-2,75; 24,77</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>-18,61; 6,27</t>
+          <t>-19,63; 5,37</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-18,8; 5,82</t>
+          <t>-18,46; 6,84</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-4,29; 16,33</t>
+          <t>-3,9; 17,16</t>
         </is>
       </c>
     </row>
@@ -1863,47 +1863,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-45,65; 61,67</t>
+          <t>-47,48; 59,19</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-51,02; 49,16</t>
+          <t>-52,75; 35,96</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-29,26; 66,59</t>
+          <t>-29,65; 70,98</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-54,91; 17,93</t>
+          <t>-54,06; 19,91</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-50,65; 41,75</t>
+          <t>-46,24; 44,26</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>-5,55; 83,04</t>
+          <t>-5,76; 81,33</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>-41,83; 18,92</t>
+          <t>-42,89; 16,56</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>-42,12; 17,67</t>
+          <t>-40,83; 22,03</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>-9,12; 53,86</t>
+          <t>-8,38; 55,25</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-3,03; 19,13</t>
+          <t>-3,41; 20,29</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-5,01; 16,33</t>
+          <t>-6,51; 16,08</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-9,96; 9,28</t>
+          <t>-9,12; 9,77</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-10,88; 12,74</t>
+          <t>-10,44; 13,54</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-3,75; 21,27</t>
+          <t>-3,14; 20,83</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-40,21; 9,04</t>
+          <t>-34,86; 9,27</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>-4,41; 12,95</t>
+          <t>-3,38; 13,33</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-0,43; 16,65</t>
+          <t>0,23; 16,14</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>-27,39; 5,07</t>
+          <t>-26,45; 5,03</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-15,19; 135,82</t>
+          <t>-16,38; 150,43</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-21,51; 125,14</t>
+          <t>-26,93; 119,71</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-40,83; 72,12</t>
+          <t>-39,88; 72,3</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-28,07; 47,42</t>
+          <t>-25,95; 50,73</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-9,62; 82,24</t>
+          <t>-8,24; 76,95</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-86,65; 29,61</t>
+          <t>-89,98; 29,74</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>-14,12; 60,79</t>
+          <t>-11,89; 58,4</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>-1,25; 77,67</t>
+          <t>0,19; 72,1</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>-82,66; 20,44</t>
+          <t>-81,76; 21,09</t>
         </is>
       </c>
     </row>
@@ -2189,47 +2189,47 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>-26,77; -3,04</t>
+          <t>-26,27; -3,16</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>-23,72; -2,18</t>
+          <t>-24,01; -1,95</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>-28,03; -9,35</t>
+          <t>-28,46; -8,57</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>-11,48; 10,48</t>
+          <t>-12,97; 8,94</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>-10,38; 12,87</t>
+          <t>-10,22; 12,13</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>-5,54; 13,47</t>
+          <t>-4,5; 13,13</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>-15,24; 0,77</t>
+          <t>-14,8; 0,9</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>-12,96; 2,71</t>
+          <t>-13,89; 2,19</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>-12,5; 1,38</t>
+          <t>-13,69; 0,09</t>
         </is>
       </c>
     </row>
@@ -2295,47 +2295,47 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>-70,02; -9,37</t>
+          <t>-69,5; -12,31</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>-62,46; -7,39</t>
+          <t>-64,5; -7,08</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>-72,03; -36,55</t>
+          <t>-72,94; -33,38</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>-30,28; 43,07</t>
+          <t>-34,98; 32,32</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>-28,0; 49,49</t>
+          <t>-26,86; 46,26</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>-14,84; 53,82</t>
+          <t>-12,73; 53,63</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>-41,92; 3,5</t>
+          <t>-41,17; 3,55</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>-36,89; 10,22</t>
+          <t>-39,09; 7,71</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>-34,24; 5,21</t>
+          <t>-36,6; 0,76</t>
         </is>
       </c>
     </row>
@@ -2405,47 +2405,47 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>-4,59; 6,5</t>
+          <t>-5,02; 5,44</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>-10,09; -0,37</t>
+          <t>-10,56; -0,32</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>-5,73; 3,8</t>
+          <t>-5,88; 3,79</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>-0,81; 10,08</t>
+          <t>-1,09; 9,36</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>-4,1; 6,19</t>
+          <t>-3,92; 6,94</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>-18,01; 8,45</t>
+          <t>-17,04; 8,69</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>-1,84; 6,43</t>
+          <t>-1,55; 6,28</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>-5,21; 2,3</t>
+          <t>-5,32; 1,86</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>-11,56; 4,48</t>
+          <t>-11,76; 4,64</t>
         </is>
       </c>
     </row>
@@ -2511,47 +2511,47 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>-16,17; 27,87</t>
+          <t>-17,45; 23,0</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>-34,16; -1,34</t>
+          <t>-35,8; -1,19</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>-19,63; 16,93</t>
+          <t>-20,14; 16,09</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>-2,19; 31,6</t>
+          <t>-2,88; 29,22</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>-11,26; 19,51</t>
+          <t>-10,46; 22,27</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>-51,56; 25,93</t>
+          <t>-48,21; 25,9</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>-5,51; 22,39</t>
+          <t>-4,77; 21,2</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>-15,82; 7,81</t>
+          <t>-16,09; 6,43</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>-34,23; 14,71</t>
+          <t>-35,96; 15,48</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/LAWTONB_2R2-Provincia-trans_camb.xlsx
+++ b/data/trans_camb/LAWTONB_2R2-Provincia-trans_camb.xlsx
@@ -634,7 +634,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>25,16</t>
+          <t>24,56</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -649,7 +649,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>26,43</t>
+          <t>26,02</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>25,84</t>
+          <t>25,3</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-15,12; 25,42</t>
+          <t>-14,34; 26,16</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-20,78; 17,15</t>
+          <t>-20,23; 16,93</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>4,9; 40,31</t>
+          <t>2,39; 39,87</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>15,2; 55,2</t>
+          <t>11,85; 53,95</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>4,55; 47,39</t>
+          <t>4,66; 45,94</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>6,2; 40,39</t>
+          <t>7,69; 40,84</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>6,34; 34,97</t>
+          <t>6,7; 36,38</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,32; 28,81</t>
+          <t>-1,59; 27,45</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>12,88; 36,96</t>
+          <t>12,78; 36,13</t>
         </is>
       </c>
     </row>
@@ -740,7 +740,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>102,69%</t>
+          <t>100,23%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>101,25%</t>
+          <t>99,66%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>101,97%</t>
+          <t>99,82%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-44,68; 196,25</t>
+          <t>-40,36; 192,84</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-57,65; 106,28</t>
+          <t>-62,02; 124,06</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>11,11; 297,26</t>
+          <t>6,0; 313,79</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>35,33; 397,47</t>
+          <t>32,02; 388,33</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>9,12; 337,83</t>
+          <t>11,65; 323,34</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>16,9; 287,14</t>
+          <t>19,09; 274,88</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>19,5; 189,06</t>
+          <t>20,78; 196,33</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,91; 184,96</t>
+          <t>-6,09; 147,64</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>36,85; 224,48</t>
+          <t>35,35; 219,92</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>-4,14</t>
+          <t>-4,54</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>21,4</t>
+          <t>22,02</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>11,58</t>
+          <t>11,55</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-10,52; 21,51</t>
+          <t>-10,08; 22,32</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-22,94; 3,71</t>
+          <t>-22,43; 4,63</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-17,75; 10,59</t>
+          <t>-16,78; 8,64</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>6,77; 31,89</t>
+          <t>6,04; 31,69</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-3,67; 23,23</t>
+          <t>-2,9; 23,52</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>9,12; 30,86</t>
+          <t>10,35; 32,68</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>3,47; 23,3</t>
+          <t>2,85; 24,07</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-7,51; 11,67</t>
+          <t>-7,95; 11,59</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>2,17; 19,66</t>
+          <t>2,72; 19,71</t>
         </is>
       </c>
     </row>
@@ -956,7 +956,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>-16,97%</t>
+          <t>-18,57%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>92,25%</t>
+          <t>94,89%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>48,88%</t>
+          <t>48,76%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-35,36; 135,05</t>
+          <t>-33,15; 141,22</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-67,09; 28,39</t>
+          <t>-68,64; 31,44</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-54,2; 69,23</t>
+          <t>-54,84; 57,97</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>24,88; 194,06</t>
+          <t>17,91; 188,93</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-13,48; 130,55</t>
+          <t>-10,1; 140,95</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>27,42; 183,09</t>
+          <t>32,44; 195,25</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>11,66; 124,66</t>
+          <t>9,88; 138,49</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-26,21; 62,72</t>
+          <t>-27,89; 63,84</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>7,25; 106,15</t>
+          <t>9,57; 111,31</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>16,11</t>
+          <t>16,06</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>8,89</t>
+          <t>9,91</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>10,42</t>
+          <t>10,94</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-10,82; 20,56</t>
+          <t>-10,78; 23,05</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-12,45; 17,07</t>
+          <t>-12,66; 15,45</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1,78; 29,64</t>
+          <t>0,49; 28,25</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-25,51; 7,43</t>
+          <t>-25,15; 5,93</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-36,53; -5,94</t>
+          <t>-35,45; -6,43</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-4,42; 22,21</t>
+          <t>-4,2; 21,71</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-15,13; 7,29</t>
+          <t>-15,22; 7,37</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-22,23; -1,22</t>
+          <t>-22,52; -1,54</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0,35; 20,41</t>
+          <t>0,35; 21,21</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1172,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>78,75%</t>
+          <t>78,49%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>20,76%</t>
+          <t>23,15%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>30,35%</t>
+          <t>31,87%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-44,49; 156,66</t>
+          <t>-37,25; 185,14</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-43,43; 144,74</t>
+          <t>-42,18; 121,84</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1,83; 256,08</t>
+          <t>-1,03; 224,06</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-50,15; 22,69</t>
+          <t>-51,58; 17,99</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-72,08; -15,36</t>
+          <t>-72,46; -16,49</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-8,28; 66,52</t>
+          <t>-7,57; 65,74</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-39,0; 24,45</t>
+          <t>-38,06; 26,28</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-56,8; -5,61</t>
+          <t>-59,09; -5,73</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>1,11; 76,14</t>
+          <t>0,71; 76,74</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>-3,89</t>
+          <t>-4,83</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>-8,98</t>
+          <t>-9,26</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>-6,67</t>
+          <t>-7,35</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-11,03; 20,97</t>
+          <t>-10,87; 22,53</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-19,92; 10,08</t>
+          <t>-18,53; 13,36</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-17,77; 9,62</t>
+          <t>-17,95; 8,22</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-13,13; 18,64</t>
+          <t>-11,76; 18,4</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-27,19; 4,82</t>
+          <t>-27,84; 3,41</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-21,56; 2,88</t>
+          <t>-22,55; 3,63</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-7,43; 16,73</t>
+          <t>-8,32; 15,7</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-19,39; 2,49</t>
+          <t>-20,04; 2,24</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-16,09; 2,94</t>
+          <t>-16,99; 2,53</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>-14,22%</t>
+          <t>-17,64%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>-20,36%</t>
+          <t>-20,98%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>-18,02%</t>
+          <t>-19,87%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-31,37; 121,33</t>
+          <t>-30,42; 113,4</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-55,64; 47,99</t>
+          <t>-52,74; 72,29</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-48,36; 49,44</t>
+          <t>-51,72; 47,11</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-24,48; 52,65</t>
+          <t>-23,84; 50,53</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-53,05; 16,54</t>
+          <t>-54,44; 9,64</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-40,29; 8,47</t>
+          <t>-41,45; 11,52</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-17,77; 54,24</t>
+          <t>-18,76; 50,44</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-45,83; 8,25</t>
+          <t>-47,71; 7,76</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-36,43; 10,95</t>
+          <t>-38,67; 9,34</t>
         </is>
       </c>
     </row>
@@ -1498,7 +1498,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>-3,61</t>
+          <t>-4,17</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -1513,7 +1513,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>-8,55</t>
+          <t>-8,47</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>-6,34</t>
+          <t>-6,51</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-24,62; 21,8</t>
+          <t>-23,3; 23,42</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-38,44; -1,8</t>
+          <t>-36,3; -0,42</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-24,35; 12,89</t>
+          <t>-24,46; 12,63</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-8,12; 34,51</t>
+          <t>-6,34; 35,73</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-11,31; 29,38</t>
+          <t>-10,62; 30,2</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-25,66; 7,07</t>
+          <t>-25,41; 9,52</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-8,99; 22,59</t>
+          <t>-8,22; 23,1</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-17,73; 12,65</t>
+          <t>-16,98; 12,07</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-19,81; 5,52</t>
+          <t>-18,49; 7,47</t>
         </is>
       </c>
     </row>
@@ -1604,7 +1604,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>-12,26%</t>
+          <t>-14,17%</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -1619,7 +1619,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>-22,57%</t>
+          <t>-22,38%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>-18,45%</t>
+          <t>-18,95%</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-63,1; 136,29</t>
+          <t>-61,62; 136,49</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-88,0; 2,08</t>
+          <t>-86,19; 10,61</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-56,53; 78,04</t>
+          <t>-56,41; 70,66</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-16,78; 127,5</t>
+          <t>-15,49; 131,22</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-23,5; 107,73</t>
+          <t>-23,64; 122,58</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-49,46; 31,32</t>
+          <t>-50,04; 41,33</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-21,97; 87,57</t>
+          <t>-20,61; 89,02</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-41,04; 48,21</t>
+          <t>-41,03; 48,0</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-45,19; 22,38</t>
+          <t>-44,02; 30,69</t>
         </is>
       </c>
     </row>
@@ -1714,7 +1714,7 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>1,78</t>
+          <t>1,89</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
@@ -1729,7 +1729,7 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>11,67</t>
+          <t>11,08</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
@@ -1744,7 +1744,7 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>6,75</t>
+          <t>6,59</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-21,98; 16,43</t>
+          <t>-22,01; 16,42</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-26,78; 10,12</t>
+          <t>-23,72; 10,31</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-14,61; 18,86</t>
+          <t>-13,38; 17,29</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-25,51; 5,5</t>
+          <t>-26,25; 6,44</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-21,56; 13,51</t>
+          <t>-22,88; 14,8</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-2,75; 24,77</t>
+          <t>-4,13; 24,23</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>-19,63; 5,37</t>
+          <t>-18,22; 5,32</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-18,46; 6,84</t>
+          <t>-18,28; 6,57</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-3,9; 17,16</t>
+          <t>-4,26; 16,81</t>
         </is>
       </c>
     </row>
@@ -1820,7 +1820,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>4,67%</t>
+          <t>4,97%</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -1835,7 +1835,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>29,35%</t>
+          <t>27,86%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -1850,7 +1850,7 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>17,28%</t>
+          <t>16,85%</t>
         </is>
       </c>
     </row>
@@ -1863,47 +1863,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-47,48; 59,19</t>
+          <t>-47,6; 57,77</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-52,75; 35,96</t>
+          <t>-49,98; 40,46</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-29,65; 70,98</t>
+          <t>-27,09; 66,4</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-54,06; 19,91</t>
+          <t>-53,75; 21,67</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-46,24; 44,26</t>
+          <t>-47,89; 49,83</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>-5,76; 81,33</t>
+          <t>-9,06; 77,67</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>-42,89; 16,56</t>
+          <t>-39,89; 16,65</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>-40,83; 22,03</t>
+          <t>-40,69; 19,15</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>-8,38; 55,25</t>
+          <t>-9,56; 51,77</t>
         </is>
       </c>
     </row>
@@ -1930,7 +1930,7 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>-0,01</t>
+          <t>0,04</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
@@ -1945,7 +1945,7 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>-17,92</t>
+          <t>5,89</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>-10,02</t>
+          <t>3,0</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-3,41; 20,29</t>
+          <t>-3,5; 19,29</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-6,51; 16,08</t>
+          <t>-3,98; 16,95</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-9,12; 9,77</t>
+          <t>-9,37; 9,31</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-10,44; 13,54</t>
+          <t>-10,73; 13,69</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-3,14; 20,83</t>
+          <t>-3,61; 20,85</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-34,86; 9,27</t>
+          <t>-3,95; 16,7</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>-3,38; 13,33</t>
+          <t>-3,46; 12,92</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>0,23; 16,14</t>
+          <t>-1,18; 16,39</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>-26,45; 5,03</t>
+          <t>-4,26; 10,15</t>
         </is>
       </c>
     </row>
@@ -2036,7 +2036,7 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>-0,06%</t>
+          <t>0,22%</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
@@ -2051,7 +2051,7 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>-53,58%</t>
+          <t>17,6%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
@@ -2066,7 +2066,7 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>-38,07%</t>
+          <t>11,39%</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-16,38; 150,43</t>
+          <t>-15,6; 142,76</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-26,93; 119,71</t>
+          <t>-19,6; 128,27</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-39,88; 72,3</t>
+          <t>-39,99; 75,64</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-25,95; 50,73</t>
+          <t>-27,71; 50,94</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-8,24; 76,95</t>
+          <t>-8,78; 77,6</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-89,98; 29,74</t>
+          <t>-10,38; 62,55</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>-11,89; 58,4</t>
+          <t>-12,66; 58,03</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>0,19; 72,1</t>
+          <t>-4,93; 72,85</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>-81,76; 21,09</t>
+          <t>-13,2; 48,49</t>
         </is>
       </c>
     </row>
@@ -2146,7 +2146,7 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>-18,36</t>
+          <t>-17,96</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
@@ -2161,7 +2161,7 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>3,9</t>
+          <t>4,44</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>-5,83</t>
+          <t>-5,23</t>
         </is>
       </c>
     </row>
@@ -2189,47 +2189,47 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>-26,27; -3,16</t>
+          <t>-25,77; -3,33</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>-24,01; -1,95</t>
+          <t>-24,69; -3,25</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>-28,46; -8,57</t>
+          <t>-27,84; -8,59</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>-12,97; 8,94</t>
+          <t>-12,25; 9,41</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>-10,22; 12,13</t>
+          <t>-9,61; 11,64</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>-4,5; 13,13</t>
+          <t>-4,72; 13,75</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>-14,8; 0,9</t>
+          <t>-14,56; 0,63</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>-13,89; 2,19</t>
+          <t>-13,7; 2,36</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>-13,69; 0,09</t>
+          <t>-11,66; 1,72</t>
         </is>
       </c>
     </row>
@@ -2252,7 +2252,7 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>-57,72%</t>
+          <t>-56,44%</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
@@ -2267,7 +2267,7 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>12,33%</t>
+          <t>14,01%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
@@ -2282,7 +2282,7 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>-18,39%</t>
+          <t>-16,47%</t>
         </is>
       </c>
     </row>
@@ -2295,47 +2295,47 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>-69,5; -12,31</t>
+          <t>-68,34; -8,45</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>-64,5; -7,08</t>
+          <t>-64,85; -11,86</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>-72,94; -33,38</t>
+          <t>-71,37; -31,92</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>-34,98; 32,32</t>
+          <t>-34,18; 36,11</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>-26,86; 46,26</t>
+          <t>-26,65; 42,11</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>-12,73; 53,63</t>
+          <t>-12,91; 52,73</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>-41,17; 3,55</t>
+          <t>-41,65; 3,26</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>-39,09; 7,71</t>
+          <t>-38,28; 8,51</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>-36,6; 0,76</t>
+          <t>-32,62; 6,24</t>
         </is>
       </c>
     </row>
@@ -2362,7 +2362,7 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>-1,02</t>
+          <t>-1,61</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
@@ -2377,7 +2377,7 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>-1,27</t>
+          <t>6,89</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
@@ -2392,7 +2392,7 @@
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>-0,84</t>
+          <t>3,01</t>
         </is>
       </c>
     </row>
@@ -2405,47 +2405,47 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>-5,02; 5,44</t>
+          <t>-5,03; 5,95</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>-10,56; -0,32</t>
+          <t>-10,62; -0,86</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>-5,88; 3,79</t>
+          <t>-6,64; 3,29</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>-1,09; 9,36</t>
+          <t>-1,06; 9,61</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>-3,92; 6,94</t>
+          <t>-4,02; 6,8</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>-17,04; 8,69</t>
+          <t>2,34; 11,58</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>-1,55; 6,28</t>
+          <t>-1,7; 6,01</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>-5,32; 1,86</t>
+          <t>-5,41; 1,86</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>-11,76; 4,64</t>
+          <t>-0,16; 6,63</t>
         </is>
       </c>
     </row>
@@ -2468,7 +2468,7 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>-3,86%</t>
+          <t>-6,11%</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
@@ -2483,7 +2483,7 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>-3,68%</t>
+          <t>20,04%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
@@ -2498,7 +2498,7 @@
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>-2,71%</t>
+          <t>9,74%</t>
         </is>
       </c>
     </row>
@@ -2511,47 +2511,47 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>-17,45; 23,0</t>
+          <t>-17,24; 26,14</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>-35,8; -1,19</t>
+          <t>-35,6; -3,53</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>-20,14; 16,09</t>
+          <t>-22,15; 13,63</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>-2,88; 29,22</t>
+          <t>-3,13; 30,04</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>-10,46; 22,27</t>
+          <t>-11,17; 21,62</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>-48,21; 25,9</t>
+          <t>6,22; 37,11</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>-4,77; 21,2</t>
+          <t>-4,96; 20,82</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>-16,09; 6,43</t>
+          <t>-16,63; 6,46</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>-35,96; 15,48</t>
+          <t>-0,43; 23,27</t>
         </is>
       </c>
     </row>
